--- a/fixtures_counts.xlsx
+++ b/fixtures_counts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\letenok.DWA\Documents\streaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB384FC-090B-4767-8006-2BE95BE9E217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E0FF80-97C4-426E-B45F-F48CDB969773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="2371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="2394">
   <si>
     <t>date</t>
   </si>
@@ -7064,9 +7064,6 @@
     <t>Real Madrid 0,2</t>
   </si>
   <si>
-    <t>fc Barcelona 0,3</t>
-  </si>
-  <si>
     <t>PSV 0,3</t>
   </si>
   <si>
@@ -7094,9 +7091,6 @@
     <t>richards 0,1</t>
   </si>
   <si>
-    <t>Hobro 0,1</t>
-  </si>
-  <si>
     <t>sociedad b 0,1</t>
   </si>
   <si>
@@ -7149,6 +7143,81 @@
   </si>
   <si>
     <t>Smouha Home 0,10</t>
+  </si>
+  <si>
+    <t>Henan 0,2</t>
+  </si>
+  <si>
+    <t>madura 0,1</t>
+  </si>
+  <si>
+    <t>PersijaJakarta 0,1</t>
+  </si>
+  <si>
+    <t>aalborg 0,2</t>
+  </si>
+  <si>
+    <t>arabCon 0,1</t>
+  </si>
+  <si>
+    <t>st.johnston win</t>
+  </si>
+  <si>
+    <t>PSV</t>
+  </si>
+  <si>
+    <t>Mjallby</t>
+  </si>
+  <si>
+    <t>RealMadrid</t>
+  </si>
+  <si>
+    <t>Modena 0,7</t>
+  </si>
+  <si>
+    <t>inter 0,3</t>
+  </si>
+  <si>
+    <t>Galatasaray 0,3</t>
+  </si>
+  <si>
+    <t>Benfica 0,2</t>
+  </si>
+  <si>
+    <t>fc barcelona</t>
+  </si>
+  <si>
+    <t>Liverpool 0,2</t>
+  </si>
+  <si>
+    <t>Midtylland 0,2</t>
+  </si>
+  <si>
+    <t>Genk 0,4</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Shimizu 0,04</t>
+  </si>
+  <si>
+    <t>Machida 0,05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanfreece </t>
+  </si>
+  <si>
+    <t>Persis 0,5</t>
+  </si>
+  <si>
+    <t>Melaka 0,1</t>
+  </si>
+  <si>
+    <t>dinamiTbilisi 0,1</t>
+  </si>
+  <si>
+    <t>Pohronia 0,1</t>
   </si>
 </sst>
 </file>
@@ -7188,12 +7257,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -7250,30 +7325,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7286,7 +7361,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7596,13 +7671,13 @@
     <col min="3" max="3" width="38.77734375" customWidth="1"/>
     <col min="4" max="4" width="13.109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.88671875" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -7640,13 +7715,13 @@
       <c r="H3" t="s">
         <v>2328</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
         <v>0.66666666666666663</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="4">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="4">
         <v>0.5</v>
       </c>
     </row>
@@ -7657,9 +7732,9 @@
       <c r="B4">
         <v>7</v>
       </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -18412,30 +18487,30 @@
       <c r="B1348">
         <v>2</v>
       </c>
-      <c r="G1348" s="13" t="s">
+      <c r="G1348" s="7" t="s">
+        <v>2358</v>
+      </c>
+      <c r="H1348" s="7" t="s">
+        <v>2359</v>
+      </c>
+      <c r="I1348" s="7" t="s">
         <v>2360</v>
       </c>
-      <c r="H1348" s="13" t="s">
+      <c r="J1348" s="7" t="s">
         <v>2361</v>
       </c>
-      <c r="I1348" s="13" t="s">
+      <c r="K1348" s="7" t="s">
         <v>2362</v>
       </c>
-      <c r="J1348" s="13" t="s">
+      <c r="L1348" s="7" t="s">
         <v>2363</v>
       </c>
-      <c r="K1348" s="13" t="s">
+      <c r="M1348" s="7" t="s">
         <v>2364</v>
       </c>
-      <c r="L1348" s="13" t="s">
-        <v>2365</v>
-      </c>
-      <c r="M1348" s="13" t="s">
-        <v>2366</v>
-      </c>
-      <c r="N1348" s="13"/>
-      <c r="O1348" s="13"/>
-      <c r="P1348" s="13"/>
+      <c r="N1348" s="7"/>
+      <c r="O1348" s="7"/>
+      <c r="P1348" s="7"/>
     </row>
     <row r="1349" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1349" t="s">
@@ -18448,19 +18523,19 @@
         <v>2340</v>
       </c>
       <c r="H1349" t="s">
-        <v>2357</v>
-      </c>
-      <c r="J1349" t="s">
-        <v>2342</v>
+        <v>2355</v>
       </c>
       <c r="K1349" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="L1349" t="s">
-        <v>2344</v>
+        <v>2343</v>
+      </c>
+      <c r="N1349" t="s">
+        <v>2348</v>
       </c>
       <c r="P1349" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="1350" spans="1:16" x14ac:dyDescent="0.3">
@@ -18471,28 +18546,22 @@
         <v>9</v>
       </c>
       <c r="G1350" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="H1350" t="s">
+        <v>2349</v>
+      </c>
+      <c r="I1350" t="s">
         <v>2350</v>
       </c>
-      <c r="I1350" t="s">
+      <c r="K1350" t="s">
         <v>2351</v>
       </c>
-      <c r="J1350" t="s">
+      <c r="L1350" t="s">
         <v>2352</v>
       </c>
-      <c r="K1350" t="s">
-        <v>2353</v>
-      </c>
-      <c r="L1350" t="s">
-        <v>2354</v>
-      </c>
-      <c r="M1350" t="s">
-        <v>2349</v>
-      </c>
       <c r="N1350" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="1351" spans="1:16" x14ac:dyDescent="0.3">
@@ -18506,10 +18575,10 @@
         <v>2341</v>
       </c>
       <c r="H1351" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="L1351" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="1352" spans="1:16" x14ac:dyDescent="0.3">
@@ -18520,10 +18589,16 @@
         <v>2</v>
       </c>
       <c r="G1352" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="H1352" t="s">
-        <v>2356</v>
+        <v>2354</v>
+      </c>
+      <c r="K1352" t="s">
+        <v>2390</v>
+      </c>
+      <c r="N1352" t="s">
+        <v>2378</v>
       </c>
     </row>
     <row r="1353" spans="1:16" x14ac:dyDescent="0.3">
@@ -18534,10 +18609,16 @@
         <v>2</v>
       </c>
       <c r="G1353" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="H1353" t="s">
-        <v>2370</v>
+        <v>2368</v>
+      </c>
+      <c r="K1353" t="s">
+        <v>2369</v>
+      </c>
+      <c r="M1353" t="s">
+        <v>2379</v>
       </c>
     </row>
     <row r="1354" spans="1:16" x14ac:dyDescent="0.3">
@@ -18548,7 +18629,13 @@
         <v>1</v>
       </c>
       <c r="G1354" t="s">
-        <v>2347</v>
+        <v>2346</v>
+      </c>
+      <c r="K1354" t="s">
+        <v>2370</v>
+      </c>
+      <c r="M1354" t="s">
+        <v>2380</v>
       </c>
     </row>
     <row r="1355" spans="1:16" x14ac:dyDescent="0.3">
@@ -18562,7 +18649,16 @@
         <v>2336</v>
       </c>
       <c r="G1355" t="s">
-        <v>2355</v>
+        <v>2353</v>
+      </c>
+      <c r="K1355" t="s">
+        <v>2371</v>
+      </c>
+      <c r="M1355" t="s">
+        <v>2383</v>
+      </c>
+      <c r="N1355" s="18" t="s">
+        <v>2381</v>
       </c>
     </row>
     <row r="1356" spans="1:16" x14ac:dyDescent="0.3">
@@ -18577,7 +18673,13 @@
         <v>2337</v>
       </c>
       <c r="G1356" t="s">
-        <v>2358</v>
+        <v>2356</v>
+      </c>
+      <c r="K1356" t="s">
+        <v>2391</v>
+      </c>
+      <c r="N1356" t="s">
+        <v>2382</v>
       </c>
     </row>
     <row r="1357" spans="1:16" x14ac:dyDescent="0.3">
@@ -18591,6 +18693,15 @@
       <c r="D1357" s="17"/>
       <c r="E1357" s="17" t="s">
         <v>2338</v>
+      </c>
+      <c r="K1357" t="s">
+        <v>2392</v>
+      </c>
+      <c r="M1357" t="s">
+        <v>2385</v>
+      </c>
+      <c r="N1357" t="s">
+        <v>2386</v>
       </c>
     </row>
     <row r="1358" spans="1:16" x14ac:dyDescent="0.3">
@@ -18606,8 +18717,17 @@
       <c r="F1358" s="17" t="s">
         <v>2339</v>
       </c>
-      <c r="G1358" s="18">
+      <c r="G1358" s="8">
         <v>4</v>
+      </c>
+      <c r="K1358" t="s">
+        <v>2393</v>
+      </c>
+      <c r="L1358" t="s">
+        <v>2374</v>
+      </c>
+      <c r="N1358" t="s">
+        <v>2384</v>
       </c>
     </row>
     <row r="1359" spans="1:16" x14ac:dyDescent="0.3">
@@ -18621,6 +18741,12 @@
       <c r="D1359" s="17"/>
       <c r="E1359" s="17"/>
       <c r="F1359" s="17"/>
+      <c r="K1359" t="s">
+        <v>2372</v>
+      </c>
+      <c r="L1359" t="s">
+        <v>2375</v>
+      </c>
     </row>
     <row r="1360" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1360" t="s">
@@ -18632,8 +18758,14 @@
       <c r="C1360" s="17"/>
       <c r="D1360" s="17"/>
       <c r="E1360" s="17"/>
-    </row>
-    <row r="1361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K1360" t="s">
+        <v>2373</v>
+      </c>
+      <c r="L1360" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1361" t="s">
         <v>963</v>
       </c>
@@ -18642,8 +18774,11 @@
       </c>
       <c r="C1361" s="17"/>
       <c r="D1361" s="17"/>
-    </row>
-    <row r="1362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="L1361" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1362" t="s">
         <v>962</v>
       </c>
@@ -18651,24 +18786,40 @@
         <v>1</v>
       </c>
       <c r="C1362" s="17"/>
-    </row>
-    <row r="1363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="M1362" t="s">
+        <v>2387</v>
+      </c>
+      <c r="N1362" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1363" t="s">
         <v>961</v>
       </c>
       <c r="B1363">
         <v>1</v>
       </c>
-    </row>
-    <row r="1364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="M1363" t="s">
+        <v>2388</v>
+      </c>
+      <c r="N1363" s="10"/>
+    </row>
+    <row r="1364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1364" t="s">
         <v>960</v>
       </c>
       <c r="B1364">
         <v>2</v>
       </c>
-    </row>
-    <row r="1365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="M1364" t="s">
+        <v>2389</v>
+      </c>
+      <c r="N1364" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1365" t="s">
         <v>959</v>
       </c>
@@ -18676,7 +18827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1366" t="s">
         <v>958</v>
       </c>
@@ -18687,7 +18838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1367" t="s">
         <v>957</v>
       </c>
@@ -18695,7 +18846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1368" t="s">
         <v>956</v>
       </c>
@@ -18703,7 +18854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1369" t="s">
         <v>955</v>
       </c>
@@ -18711,7 +18862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1370" t="s">
         <v>954</v>
       </c>
@@ -18719,7 +18870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1371" t="s">
         <v>953</v>
       </c>
@@ -18727,7 +18878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1372" t="s">
         <v>952</v>
       </c>
@@ -18735,7 +18886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1373" t="s">
         <v>951</v>
       </c>
@@ -18746,7 +18897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1374" t="s">
         <v>950</v>
       </c>
@@ -18754,7 +18905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1375" t="s">
         <v>949</v>
       </c>
@@ -18762,7 +18913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1376" t="s">
         <v>948</v>
       </c>
@@ -18823,7 +18974,7 @@
       <c r="B1382">
         <v>13</v>
       </c>
-      <c r="C1382" s="5">
+      <c r="C1382" s="3">
         <v>1</v>
       </c>
     </row>
@@ -18834,7 +18985,7 @@
       <c r="B1383">
         <v>1</v>
       </c>
-      <c r="C1383" s="4">
+      <c r="C1383" s="10">
         <v>1</v>
       </c>
     </row>
@@ -18845,7 +18996,7 @@
       <c r="B1384">
         <v>6</v>
       </c>
-      <c r="C1384" s="4"/>
+      <c r="C1384" s="10"/>
     </row>
     <row r="1385" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1385" t="s">
@@ -18854,7 +19005,7 @@
       <c r="B1385">
         <v>6</v>
       </c>
-      <c r="C1385" s="4"/>
+      <c r="C1385" s="10"/>
     </row>
     <row r="1386" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1386" t="s">
@@ -18863,7 +19014,7 @@
       <c r="B1386">
         <v>3</v>
       </c>
-      <c r="C1386" s="4"/>
+      <c r="C1386" s="10"/>
     </row>
     <row r="1387" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1387" t="s">
@@ -18872,7 +19023,7 @@
       <c r="B1387">
         <v>1</v>
       </c>
-      <c r="C1387" s="4"/>
+      <c r="C1387" s="10"/>
     </row>
     <row r="1388" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1388" t="s">
@@ -18881,7 +19032,7 @@
       <c r="B1388">
         <v>1</v>
       </c>
-      <c r="C1388" s="4"/>
+      <c r="C1388" s="10"/>
     </row>
     <row r="1389" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1389" t="s">
@@ -18932,64 +19083,64 @@
       <c r="B1391">
         <v>1</v>
       </c>
-      <c r="G1391" s="13">
-        <v>1</v>
-      </c>
-      <c r="H1391" s="13">
-        <v>2</v>
-      </c>
-      <c r="I1391" s="13">
+      <c r="G1391" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1391" s="7">
+        <v>2</v>
+      </c>
+      <c r="I1391" s="7">
         <v>3</v>
       </c>
-      <c r="J1391" s="13">
+      <c r="J1391" s="7">
         <v>4</v>
       </c>
-      <c r="K1391" s="13">
+      <c r="K1391" s="7">
         <v>5</v>
       </c>
-      <c r="L1391" s="13">
+      <c r="L1391" s="7">
         <v>6</v>
       </c>
-      <c r="M1391" s="13">
+      <c r="M1391" s="7">
         <v>7</v>
       </c>
-      <c r="N1391" s="13">
+      <c r="N1391" s="7">
         <v>8</v>
       </c>
-      <c r="O1391" s="13">
+      <c r="O1391" s="7">
         <v>9</v>
       </c>
-      <c r="P1391" s="13">
+      <c r="P1391" s="7">
         <v>10</v>
       </c>
-      <c r="Q1391" s="13">
+      <c r="Q1391" s="7">
         <v>11</v>
       </c>
-      <c r="R1391" s="13">
+      <c r="R1391" s="7">
         <v>12</v>
       </c>
-      <c r="S1391" s="13">
+      <c r="S1391" s="7">
         <v>13</v>
       </c>
-      <c r="T1391" s="13">
+      <c r="T1391" s="7">
         <v>14</v>
       </c>
-      <c r="U1391" s="13">
+      <c r="U1391" s="7">
         <v>15</v>
       </c>
-      <c r="V1391" s="13">
+      <c r="V1391" s="7">
         <v>16</v>
       </c>
-      <c r="W1391" s="13">
+      <c r="W1391" s="7">
         <v>17</v>
       </c>
-      <c r="X1391" s="13">
+      <c r="X1391" s="7">
         <v>18</v>
       </c>
-      <c r="Y1391" s="13">
+      <c r="Y1391" s="7">
         <v>19</v>
       </c>
-      <c r="Z1391" s="13">
+      <c r="Z1391" s="7">
         <v>20</v>
       </c>
     </row>
@@ -19033,7 +19184,7 @@
       <c r="B1395">
         <v>1</v>
       </c>
-      <c r="C1395" s="3">
+      <c r="C1395" s="9">
         <v>1</v>
       </c>
     </row>
@@ -19044,7 +19195,7 @@
       <c r="B1396">
         <v>1</v>
       </c>
-      <c r="C1396" s="3"/>
+      <c r="C1396" s="9"/>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1397" t="s">
@@ -19053,7 +19204,7 @@
       <c r="B1397">
         <v>4</v>
       </c>
-      <c r="C1397" s="3"/>
+      <c r="C1397" s="9"/>
     </row>
     <row r="1398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1398" t="s">
@@ -19062,7 +19213,7 @@
       <c r="B1398">
         <v>1</v>
       </c>
-      <c r="C1398" s="3"/>
+      <c r="C1398" s="9"/>
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1399" t="s">
@@ -19071,7 +19222,7 @@
       <c r="B1399">
         <v>8</v>
       </c>
-      <c r="C1399" s="4">
+      <c r="C1399" s="10">
         <v>1</v>
       </c>
     </row>
@@ -19082,7 +19233,7 @@
       <c r="B1400">
         <v>1</v>
       </c>
-      <c r="C1400" s="4"/>
+      <c r="C1400" s="10"/>
     </row>
     <row r="1401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1401" t="s">
@@ -19091,7 +19242,7 @@
       <c r="B1401">
         <v>1</v>
       </c>
-      <c r="C1401" s="4"/>
+      <c r="C1401" s="10"/>
     </row>
     <row r="1402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1402" t="s">
@@ -19100,7 +19251,7 @@
       <c r="B1402">
         <v>3</v>
       </c>
-      <c r="C1402" s="12" t="s">
+      <c r="C1402" s="13" t="s">
         <v>2330</v>
       </c>
     </row>
@@ -19111,7 +19262,7 @@
       <c r="B1403">
         <v>1</v>
       </c>
-      <c r="C1403" s="12"/>
+      <c r="C1403" s="13"/>
     </row>
     <row r="1404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1404" t="s">
@@ -19120,7 +19271,7 @@
       <c r="B1404">
         <v>1</v>
       </c>
-      <c r="C1404" s="12"/>
+      <c r="C1404" s="13"/>
     </row>
     <row r="1405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1405" t="s">
@@ -19129,7 +19280,7 @@
       <c r="B1405">
         <v>2</v>
       </c>
-      <c r="C1405" s="12"/>
+      <c r="C1405" s="13"/>
     </row>
     <row r="1406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1406" t="s">
@@ -19138,7 +19289,7 @@
       <c r="B1406">
         <v>1</v>
       </c>
-      <c r="C1406" s="12"/>
+      <c r="C1406" s="13"/>
     </row>
     <row r="1407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1407" t="s">
@@ -19147,7 +19298,7 @@
       <c r="B1407">
         <v>1</v>
       </c>
-      <c r="C1407" s="12"/>
+      <c r="C1407" s="13"/>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1408" t="s">
@@ -19156,7 +19307,7 @@
       <c r="B1408">
         <v>5</v>
       </c>
-      <c r="C1408" s="12"/>
+      <c r="C1408" s="13"/>
     </row>
     <row r="1409" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1409" t="s">
@@ -19197,16 +19348,16 @@
       <c r="B1413">
         <v>9</v>
       </c>
-      <c r="C1413" s="9" t="s">
+      <c r="C1413" s="6" t="s">
         <v>2330</v>
       </c>
-      <c r="D1413" s="9"/>
-      <c r="S1413" s="10" t="s">
+      <c r="D1413" s="6"/>
+      <c r="S1413" s="11" t="s">
         <v>2329</v>
       </c>
-      <c r="T1413" s="11"/>
-      <c r="U1413" s="11"/>
-      <c r="V1413" s="11"/>
+      <c r="T1413" s="12"/>
+      <c r="U1413" s="12"/>
+      <c r="V1413" s="12"/>
     </row>
     <row r="1414" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1414" t="s">
@@ -19271,10 +19422,9 @@
       <c r="B1421">
         <v>12</v>
       </c>
-      <c r="C1421" s="9" t="s">
+      <c r="C1421" s="6" t="s">
         <v>2330</v>
       </c>
-      <c r="D1421" s="8"/>
     </row>
     <row r="1422" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1422" t="s">
@@ -19291,10 +19441,9 @@
       <c r="B1423">
         <v>32</v>
       </c>
-      <c r="C1423" s="9" t="s">
+      <c r="C1423" s="6" t="s">
         <v>2332</v>
       </c>
-      <c r="D1423" s="8"/>
     </row>
     <row r="1424" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1424" t="s">
@@ -19311,7 +19460,7 @@
       <c r="B1425">
         <v>43</v>
       </c>
-      <c r="C1425" s="9" t="s">
+      <c r="C1425" s="6" t="s">
         <v>2331</v>
       </c>
     </row>
@@ -19338,10 +19487,10 @@
       <c r="B1428">
         <v>7</v>
       </c>
-      <c r="C1428" s="3">
+      <c r="C1428" s="9">
         <v>6</v>
       </c>
-      <c r="D1428" s="3"/>
+      <c r="D1428" s="9"/>
     </row>
     <row r="1429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1429" t="s">
@@ -19366,10 +19515,10 @@
       <c r="B1431">
         <v>11</v>
       </c>
-      <c r="C1431" s="3">
+      <c r="C1431" s="9">
         <v>5</v>
       </c>
-      <c r="D1431" s="3"/>
+      <c r="D1431" s="9"/>
     </row>
     <row r="1432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1432" t="s">
@@ -19386,10 +19535,10 @@
       <c r="B1433">
         <v>8</v>
       </c>
-      <c r="C1433" s="3">
+      <c r="C1433" s="9">
         <v>4</v>
       </c>
-      <c r="D1433" s="3"/>
+      <c r="D1433" s="9"/>
     </row>
     <row r="1434" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1434" t="s">
@@ -19414,10 +19563,10 @@
       <c r="B1436">
         <v>14</v>
       </c>
-      <c r="C1436" s="3">
+      <c r="C1436" s="9">
         <v>3</v>
       </c>
-      <c r="D1436" s="3"/>
+      <c r="D1436" s="9"/>
     </row>
     <row r="1437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1437" t="s">
@@ -19458,10 +19607,10 @@
       <c r="B1441">
         <v>7</v>
       </c>
-      <c r="C1441" s="3" t="s">
+      <c r="C1441" s="9" t="s">
         <v>2324</v>
       </c>
-      <c r="D1441" s="3"/>
+      <c r="D1441" s="9"/>
     </row>
     <row r="1442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1442" t="s">
@@ -19470,10 +19619,10 @@
       <c r="B1442">
         <v>1</v>
       </c>
-      <c r="C1442" s="3" t="s">
+      <c r="C1442" s="9" t="s">
         <v>2323</v>
       </c>
-      <c r="D1442" s="3"/>
+      <c r="D1442" s="9"/>
     </row>
     <row r="1443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1443" t="s">
@@ -19482,8 +19631,8 @@
       <c r="B1443">
         <v>1</v>
       </c>
-      <c r="C1443" s="3"/>
-      <c r="D1443" s="3"/>
+      <c r="C1443" s="9"/>
+      <c r="D1443" s="9"/>
     </row>
     <row r="1444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1444" t="s">
@@ -19492,8 +19641,8 @@
       <c r="B1444">
         <v>1</v>
       </c>
-      <c r="C1444" s="3"/>
-      <c r="D1444" s="3"/>
+      <c r="C1444" s="9"/>
+      <c r="D1444" s="9"/>
     </row>
     <row r="1445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1445" t="s">
@@ -19502,8 +19651,8 @@
       <c r="B1445">
         <v>1</v>
       </c>
-      <c r="C1445" s="3"/>
-      <c r="D1445" s="3"/>
+      <c r="C1445" s="9"/>
+      <c r="D1445" s="9"/>
     </row>
     <row r="1446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1446" t="s">
@@ -19512,8 +19661,8 @@
       <c r="B1446">
         <v>1</v>
       </c>
-      <c r="C1446" s="3"/>
-      <c r="D1446" s="3"/>
+      <c r="C1446" s="9"/>
+      <c r="D1446" s="9"/>
     </row>
     <row r="1447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1447" t="s">
@@ -19570,10 +19719,10 @@
       <c r="B1453">
         <v>13</v>
       </c>
-      <c r="C1453" s="3">
-        <v>1</v>
-      </c>
-      <c r="D1453" s="3"/>
+      <c r="C1453" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1453" s="9"/>
     </row>
     <row r="1454" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1454" t="s">
@@ -19598,10 +19747,10 @@
       <c r="B1456">
         <v>10</v>
       </c>
-      <c r="C1456" s="3">
-        <v>1</v>
-      </c>
-      <c r="D1456" s="3"/>
+      <c r="C1456" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1456" s="9"/>
     </row>
     <row r="1457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1457" t="s">
@@ -19626,10 +19775,10 @@
       <c r="B1459">
         <v>17</v>
       </c>
-      <c r="C1459" s="3">
-        <v>1</v>
-      </c>
-      <c r="D1459" s="3"/>
+      <c r="C1459" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1459" s="9"/>
     </row>
     <row r="1460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1460" t="s">
@@ -19638,10 +19787,10 @@
       <c r="B1460">
         <v>3</v>
       </c>
-      <c r="C1460" s="3">
-        <v>1</v>
-      </c>
-      <c r="D1460" s="3"/>
+      <c r="C1460" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1460" s="9"/>
     </row>
     <row r="1461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1461" t="s">
@@ -19650,8 +19799,8 @@
       <c r="B1461">
         <v>3</v>
       </c>
-      <c r="C1461" s="3"/>
-      <c r="D1461" s="3"/>
+      <c r="C1461" s="9"/>
+      <c r="D1461" s="9"/>
     </row>
     <row r="1462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1462" t="s">
@@ -19660,8 +19809,8 @@
       <c r="B1462">
         <v>2</v>
       </c>
-      <c r="C1462" s="3"/>
-      <c r="D1462" s="3"/>
+      <c r="C1462" s="9"/>
+      <c r="D1462" s="9"/>
     </row>
     <row r="1463" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1463" t="s">
@@ -19670,8 +19819,8 @@
       <c r="B1463">
         <v>2</v>
       </c>
-      <c r="C1463" s="3"/>
-      <c r="D1463" s="3"/>
+      <c r="C1463" s="9"/>
+      <c r="D1463" s="9"/>
     </row>
     <row r="1464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1464" t="s">
@@ -19680,10 +19829,10 @@
       <c r="B1464">
         <v>1</v>
       </c>
-      <c r="C1464" s="3">
-        <v>1</v>
-      </c>
-      <c r="D1464" s="3"/>
+      <c r="C1464" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1464" s="9"/>
     </row>
     <row r="1465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1465" t="s">
@@ -19692,8 +19841,8 @@
       <c r="B1465">
         <v>2</v>
       </c>
-      <c r="C1465" s="3"/>
-      <c r="D1465" s="3"/>
+      <c r="C1465" s="9"/>
+      <c r="D1465" s="9"/>
     </row>
     <row r="1466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1466" t="s">
@@ -19702,8 +19851,8 @@
       <c r="B1466">
         <v>1</v>
       </c>
-      <c r="C1466" s="3"/>
-      <c r="D1466" s="3"/>
+      <c r="C1466" s="9"/>
+      <c r="D1466" s="9"/>
     </row>
     <row r="1467" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1467" t="s">
@@ -19712,8 +19861,8 @@
       <c r="B1467">
         <v>1</v>
       </c>
-      <c r="C1467" s="3"/>
-      <c r="D1467" s="3"/>
+      <c r="C1467" s="9"/>
+      <c r="D1467" s="9"/>
     </row>
     <row r="1468" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1468" t="s">
@@ -26560,12 +26709,14 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B2322">
     <sortCondition descending="1" ref="A1:A2322"/>
   </sortState>
-  <mergeCells count="22">
+  <mergeCells count="23">
+    <mergeCell ref="N1362:N1363"/>
     <mergeCell ref="C1355:C1362"/>
     <mergeCell ref="D1356:D1361"/>
     <mergeCell ref="E1357:E1360"/>
     <mergeCell ref="F1358:F1359"/>
     <mergeCell ref="C1460:D1463"/>
+    <mergeCell ref="C1428:D1428"/>
     <mergeCell ref="C1464:D1467"/>
     <mergeCell ref="C1399:C1401"/>
     <mergeCell ref="C1395:C1398"/>
@@ -26582,7 +26733,6 @@
     <mergeCell ref="C1436:D1436"/>
     <mergeCell ref="C1433:D1433"/>
     <mergeCell ref="C1431:D1431"/>
-    <mergeCell ref="C1428:D1428"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fixtures_counts.xlsx
+++ b/fixtures_counts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\letenok.DWA\Documents\streaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E0FF80-97C4-426E-B45F-F48CDB969773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC22F2E1-AEB7-4D7B-BED2-121110CEDF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="2394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="2355">
   <si>
     <t>date</t>
   </si>
@@ -7058,60 +7058,6 @@
     <t>0,01 =0,1</t>
   </si>
   <si>
-    <t>Galatasary 0,3</t>
-  </si>
-  <si>
-    <t>Real Madrid 0,2</t>
-  </si>
-  <si>
-    <t>PSV 0,3</t>
-  </si>
-  <si>
-    <t>liverpool 0,3</t>
-  </si>
-  <si>
-    <t>zed 0,1</t>
-  </si>
-  <si>
-    <t>guon 0,3</t>
-  </si>
-  <si>
-    <t>petrojet 0,1</t>
-  </si>
-  <si>
-    <t>sevilla 0,1</t>
-  </si>
-  <si>
-    <t>falkenberg 0,1</t>
-  </si>
-  <si>
-    <t>Gallants 0,1</t>
-  </si>
-  <si>
-    <t>richards 0,1</t>
-  </si>
-  <si>
-    <t>sociedad b 0,1</t>
-  </si>
-  <si>
-    <t>west ham 0,1</t>
-  </si>
-  <si>
-    <t>Chiefs 0,1</t>
-  </si>
-  <si>
-    <t>Sandvken0,1</t>
-  </si>
-  <si>
-    <t>Liverpool 0,3</t>
-  </si>
-  <si>
-    <t>ManUtd 0,3</t>
-  </si>
-  <si>
-    <t>Almeria 0,1</t>
-  </si>
-  <si>
     <t>Mon</t>
   </si>
   <si>
@@ -7133,91 +7079,28 @@
     <t>Sun</t>
   </si>
   <si>
-    <t>Birmingham 0,1</t>
-  </si>
-  <si>
-    <t>Charlton 0,1</t>
-  </si>
-  <si>
-    <t>Orbit 0,1</t>
-  </si>
-  <si>
-    <t>Smouha Home 0,10</t>
-  </si>
-  <si>
-    <t>Henan 0,2</t>
-  </si>
-  <si>
-    <t>madura 0,1</t>
-  </si>
-  <si>
-    <t>PersijaJakarta 0,1</t>
-  </si>
-  <si>
-    <t>aalborg 0,2</t>
-  </si>
-  <si>
-    <t>arabCon 0,1</t>
-  </si>
-  <si>
-    <t>st.johnston win</t>
-  </si>
-  <si>
-    <t>PSV</t>
-  </si>
-  <si>
-    <t>Mjallby</t>
-  </si>
-  <si>
-    <t>RealMadrid</t>
-  </si>
-  <si>
-    <t>Modena 0,7</t>
-  </si>
-  <si>
-    <t>inter 0,3</t>
-  </si>
-  <si>
-    <t>Galatasaray 0,3</t>
-  </si>
-  <si>
-    <t>Benfica 0,2</t>
-  </si>
-  <si>
-    <t>fc barcelona</t>
-  </si>
-  <si>
-    <t>Liverpool 0,2</t>
-  </si>
-  <si>
-    <t>Midtylland 0,2</t>
-  </si>
-  <si>
-    <t>Genk 0,4</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Shimizu 0,04</t>
-  </si>
-  <si>
-    <t>Machida 0,05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanfreece </t>
-  </si>
-  <si>
-    <t>Persis 0,5</t>
-  </si>
-  <si>
-    <t>Melaka 0,1</t>
-  </si>
-  <si>
-    <t>dinamiTbilisi 0,1</t>
-  </si>
-  <si>
-    <t>Pohronia 0,1</t>
+    <t>Afumati</t>
+  </si>
+  <si>
+    <t>HokkaidoConsadoleSapporo under 2 1st half</t>
+  </si>
+  <si>
+    <t>polisi under 3/ 1st under 1,5</t>
+  </si>
+  <si>
+    <t>FCBihor 1stHalf under 1,5</t>
+  </si>
+  <si>
+    <t>Tunari under 1st 1,5</t>
+  </si>
+  <si>
+    <t>fc voluntair 1st 1,5 under</t>
+  </si>
+  <si>
+    <t>Utsikten 1st under 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> under 1,5 1st nurnber</t>
   </si>
 </sst>
 </file>
@@ -7334,11 +7217,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -7355,13 +7245,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7676,7 +7559,7 @@
     <col min="9" max="9" width="14.88671875" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18488,25 +18371,25 @@
         <v>2</v>
       </c>
       <c r="G1348" s="7" t="s">
-        <v>2358</v>
+        <v>2340</v>
       </c>
       <c r="H1348" s="7" t="s">
-        <v>2359</v>
+        <v>2341</v>
       </c>
       <c r="I1348" s="7" t="s">
-        <v>2360</v>
+        <v>2342</v>
       </c>
       <c r="J1348" s="7" t="s">
-        <v>2361</v>
+        <v>2343</v>
       </c>
       <c r="K1348" s="7" t="s">
-        <v>2362</v>
+        <v>2344</v>
       </c>
       <c r="L1348" s="7" t="s">
-        <v>2363</v>
+        <v>2345</v>
       </c>
       <c r="M1348" s="7" t="s">
-        <v>2364</v>
+        <v>2346</v>
       </c>
       <c r="N1348" s="7"/>
       <c r="O1348" s="7"/>
@@ -18519,22 +18402,7 @@
       <c r="B1349">
         <v>1</v>
       </c>
-      <c r="G1349" t="s">
-        <v>2340</v>
-      </c>
-      <c r="H1349" t="s">
-        <v>2355</v>
-      </c>
-      <c r="K1349" t="s">
-        <v>2365</v>
-      </c>
       <c r="L1349" t="s">
-        <v>2343</v>
-      </c>
-      <c r="N1349" t="s">
-        <v>2348</v>
-      </c>
-      <c r="P1349" t="s">
         <v>2347</v>
       </c>
     </row>
@@ -18545,23 +18413,8 @@
       <c r="B1350">
         <v>9</v>
       </c>
-      <c r="G1350" t="s">
-        <v>2345</v>
-      </c>
-      <c r="H1350" t="s">
-        <v>2349</v>
-      </c>
-      <c r="I1350" t="s">
-        <v>2350</v>
-      </c>
-      <c r="K1350" t="s">
-        <v>2351</v>
-      </c>
       <c r="L1350" t="s">
-        <v>2352</v>
-      </c>
-      <c r="N1350" t="s">
-        <v>2357</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1351" spans="1:16" x14ac:dyDescent="0.3">
@@ -18571,14 +18424,8 @@
       <c r="B1351">
         <v>8</v>
       </c>
-      <c r="G1351" t="s">
-        <v>2341</v>
-      </c>
-      <c r="H1351" t="s">
-        <v>2367</v>
-      </c>
       <c r="L1351" t="s">
-        <v>2366</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1352" spans="1:16" x14ac:dyDescent="0.3">
@@ -18588,17 +18435,8 @@
       <c r="B1352">
         <v>2</v>
       </c>
-      <c r="G1352" t="s">
-        <v>2342</v>
-      </c>
-      <c r="H1352" t="s">
-        <v>2354</v>
-      </c>
-      <c r="K1352" t="s">
-        <v>2390</v>
-      </c>
-      <c r="N1352" t="s">
-        <v>2378</v>
+      <c r="L1352" t="s">
+        <v>2350</v>
       </c>
     </row>
     <row r="1353" spans="1:16" x14ac:dyDescent="0.3">
@@ -18608,17 +18446,8 @@
       <c r="B1353">
         <v>2</v>
       </c>
-      <c r="G1353" t="s">
-        <v>2344</v>
-      </c>
-      <c r="H1353" t="s">
-        <v>2368</v>
-      </c>
-      <c r="K1353" t="s">
-        <v>2369</v>
-      </c>
-      <c r="M1353" t="s">
-        <v>2379</v>
+      <c r="L1353" t="s">
+        <v>2351</v>
       </c>
     </row>
     <row r="1354" spans="1:16" x14ac:dyDescent="0.3">
@@ -18628,14 +18457,8 @@
       <c r="B1354">
         <v>1</v>
       </c>
-      <c r="G1354" t="s">
-        <v>2346</v>
-      </c>
-      <c r="K1354" t="s">
-        <v>2370</v>
-      </c>
-      <c r="M1354" t="s">
-        <v>2380</v>
+      <c r="L1354" t="s">
+        <v>2352</v>
       </c>
     </row>
     <row r="1355" spans="1:16" x14ac:dyDescent="0.3">
@@ -18645,21 +18468,13 @@
       <c r="B1355">
         <v>1</v>
       </c>
-      <c r="C1355" s="16" t="s">
+      <c r="C1355" s="11" t="s">
         <v>2336</v>
       </c>
-      <c r="G1355" t="s">
+      <c r="L1355" t="s">
         <v>2353</v>
       </c>
-      <c r="K1355" t="s">
-        <v>2371</v>
-      </c>
-      <c r="M1355" t="s">
-        <v>2383</v>
-      </c>
-      <c r="N1355" s="18" t="s">
-        <v>2381</v>
-      </c>
+      <c r="N1355" s="9"/>
     </row>
     <row r="1356" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1356" t="s">
@@ -18668,18 +18483,12 @@
       <c r="B1356">
         <v>1</v>
       </c>
-      <c r="C1356" s="17"/>
-      <c r="D1356" s="17" t="s">
+      <c r="C1356" s="12"/>
+      <c r="D1356" s="12" t="s">
         <v>2337</v>
       </c>
-      <c r="G1356" t="s">
-        <v>2356</v>
-      </c>
-      <c r="K1356" t="s">
-        <v>2391</v>
-      </c>
-      <c r="N1356" t="s">
-        <v>2382</v>
+      <c r="L1356" t="s">
+        <v>2354</v>
       </c>
     </row>
     <row r="1357" spans="1:16" x14ac:dyDescent="0.3">
@@ -18689,19 +18498,10 @@
       <c r="B1357">
         <v>1</v>
       </c>
-      <c r="C1357" s="17"/>
-      <c r="D1357" s="17"/>
-      <c r="E1357" s="17" t="s">
+      <c r="C1357" s="12"/>
+      <c r="D1357" s="12"/>
+      <c r="E1357" s="12" t="s">
         <v>2338</v>
-      </c>
-      <c r="K1357" t="s">
-        <v>2392</v>
-      </c>
-      <c r="M1357" t="s">
-        <v>2385</v>
-      </c>
-      <c r="N1357" t="s">
-        <v>2386</v>
       </c>
     </row>
     <row r="1358" spans="1:16" x14ac:dyDescent="0.3">
@@ -18711,23 +18511,14 @@
       <c r="B1358">
         <v>2</v>
       </c>
-      <c r="C1358" s="17"/>
-      <c r="D1358" s="17"/>
-      <c r="E1358" s="17"/>
-      <c r="F1358" s="17" t="s">
+      <c r="C1358" s="12"/>
+      <c r="D1358" s="12"/>
+      <c r="E1358" s="12"/>
+      <c r="F1358" s="12" t="s">
         <v>2339</v>
       </c>
       <c r="G1358" s="8">
         <v>4</v>
-      </c>
-      <c r="K1358" t="s">
-        <v>2393</v>
-      </c>
-      <c r="L1358" t="s">
-        <v>2374</v>
-      </c>
-      <c r="N1358" t="s">
-        <v>2384</v>
       </c>
     </row>
     <row r="1359" spans="1:16" x14ac:dyDescent="0.3">
@@ -18737,16 +18528,10 @@
       <c r="B1359">
         <v>1</v>
       </c>
-      <c r="C1359" s="17"/>
-      <c r="D1359" s="17"/>
-      <c r="E1359" s="17"/>
-      <c r="F1359" s="17"/>
-      <c r="K1359" t="s">
-        <v>2372</v>
-      </c>
-      <c r="L1359" t="s">
-        <v>2375</v>
-      </c>
+      <c r="C1359" s="12"/>
+      <c r="D1359" s="12"/>
+      <c r="E1359" s="12"/>
+      <c r="F1359" s="12"/>
     </row>
     <row r="1360" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1360" t="s">
@@ -18755,15 +18540,9 @@
       <c r="B1360">
         <v>1</v>
       </c>
-      <c r="C1360" s="17"/>
-      <c r="D1360" s="17"/>
-      <c r="E1360" s="17"/>
-      <c r="K1360" t="s">
-        <v>2373</v>
-      </c>
-      <c r="L1360" t="s">
-        <v>2376</v>
-      </c>
+      <c r="C1360" s="12"/>
+      <c r="D1360" s="12"/>
+      <c r="E1360" s="12"/>
     </row>
     <row r="1361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1361" t="s">
@@ -18772,11 +18551,8 @@
       <c r="B1361">
         <v>2</v>
       </c>
-      <c r="C1361" s="17"/>
-      <c r="D1361" s="17"/>
-      <c r="L1361" t="s">
-        <v>2377</v>
-      </c>
+      <c r="C1361" s="12"/>
+      <c r="D1361" s="12"/>
     </row>
     <row r="1362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1362" t="s">
@@ -18785,13 +18561,8 @@
       <c r="B1362">
         <v>1</v>
       </c>
-      <c r="C1362" s="17"/>
-      <c r="M1362" t="s">
-        <v>2387</v>
-      </c>
-      <c r="N1362" s="10">
-        <v>0.1</v>
-      </c>
+      <c r="C1362" s="12"/>
+      <c r="N1362" s="10"/>
     </row>
     <row r="1363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1363" t="s">
@@ -18800,9 +18571,6 @@
       <c r="B1363">
         <v>1</v>
       </c>
-      <c r="M1363" t="s">
-        <v>2388</v>
-      </c>
       <c r="N1363" s="10"/>
     </row>
     <row r="1364" spans="1:14" x14ac:dyDescent="0.3">
@@ -18812,12 +18580,7 @@
       <c r="B1364">
         <v>2</v>
       </c>
-      <c r="M1364" t="s">
-        <v>2389</v>
-      </c>
-      <c r="N1364" s="2">
-        <v>0.2</v>
-      </c>
+      <c r="N1364" s="2"/>
     </row>
     <row r="1365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1365" t="s">
@@ -19052,29 +18815,29 @@
       <c r="C1390" s="2">
         <v>1</v>
       </c>
-      <c r="G1390" s="14" t="s">
+      <c r="G1390" s="17" t="s">
         <v>2333</v>
       </c>
-      <c r="H1390" s="14"/>
-      <c r="I1390" s="14"/>
-      <c r="J1390" s="14"/>
-      <c r="K1390" s="14"/>
-      <c r="L1390" s="14"/>
-      <c r="M1390" s="14"/>
-      <c r="N1390" s="14"/>
-      <c r="O1390" s="14"/>
-      <c r="P1390" s="14"/>
-      <c r="Q1390" s="14"/>
-      <c r="R1390" s="14"/>
-      <c r="S1390" s="14"/>
-      <c r="T1390" s="14"/>
-      <c r="U1390" s="14"/>
-      <c r="V1390" s="14"/>
-      <c r="W1390" s="14"/>
-      <c r="X1390" s="14"/>
-      <c r="Y1390" s="14"/>
-      <c r="Z1390" s="14"/>
-      <c r="AA1390" s="14"/>
+      <c r="H1390" s="17"/>
+      <c r="I1390" s="17"/>
+      <c r="J1390" s="17"/>
+      <c r="K1390" s="17"/>
+      <c r="L1390" s="17"/>
+      <c r="M1390" s="17"/>
+      <c r="N1390" s="17"/>
+      <c r="O1390" s="17"/>
+      <c r="P1390" s="17"/>
+      <c r="Q1390" s="17"/>
+      <c r="R1390" s="17"/>
+      <c r="S1390" s="17"/>
+      <c r="T1390" s="17"/>
+      <c r="U1390" s="17"/>
+      <c r="V1390" s="17"/>
+      <c r="W1390" s="17"/>
+      <c r="X1390" s="17"/>
+      <c r="Y1390" s="17"/>
+      <c r="Z1390" s="17"/>
+      <c r="AA1390" s="17"/>
     </row>
     <row r="1391" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1391" t="s">
@@ -19154,12 +18917,12 @@
       <c r="G1392" t="s">
         <v>2334</v>
       </c>
-      <c r="H1392" s="15" t="s">
+      <c r="H1392" s="18" t="s">
         <v>2335</v>
       </c>
-      <c r="I1392" s="15"/>
-      <c r="J1392" s="15"/>
-      <c r="K1392" s="15"/>
+      <c r="I1392" s="18"/>
+      <c r="J1392" s="18"/>
+      <c r="K1392" s="18"/>
     </row>
     <row r="1393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1393" t="s">
@@ -19184,7 +18947,7 @@
       <c r="B1395">
         <v>1</v>
       </c>
-      <c r="C1395" s="9">
+      <c r="C1395" s="13">
         <v>1</v>
       </c>
     </row>
@@ -19195,7 +18958,7 @@
       <c r="B1396">
         <v>1</v>
       </c>
-      <c r="C1396" s="9"/>
+      <c r="C1396" s="13"/>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1397" t="s">
@@ -19204,7 +18967,7 @@
       <c r="B1397">
         <v>4</v>
       </c>
-      <c r="C1397" s="9"/>
+      <c r="C1397" s="13"/>
     </row>
     <row r="1398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1398" t="s">
@@ -19213,7 +18976,7 @@
       <c r="B1398">
         <v>1</v>
       </c>
-      <c r="C1398" s="9"/>
+      <c r="C1398" s="13"/>
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1399" t="s">
@@ -19251,7 +19014,7 @@
       <c r="B1402">
         <v>3</v>
       </c>
-      <c r="C1402" s="13" t="s">
+      <c r="C1402" s="16" t="s">
         <v>2330</v>
       </c>
     </row>
@@ -19262,7 +19025,7 @@
       <c r="B1403">
         <v>1</v>
       </c>
-      <c r="C1403" s="13"/>
+      <c r="C1403" s="16"/>
     </row>
     <row r="1404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1404" t="s">
@@ -19271,7 +19034,7 @@
       <c r="B1404">
         <v>1</v>
       </c>
-      <c r="C1404" s="13"/>
+      <c r="C1404" s="16"/>
     </row>
     <row r="1405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1405" t="s">
@@ -19280,7 +19043,7 @@
       <c r="B1405">
         <v>2</v>
       </c>
-      <c r="C1405" s="13"/>
+      <c r="C1405" s="16"/>
     </row>
     <row r="1406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1406" t="s">
@@ -19289,7 +19052,7 @@
       <c r="B1406">
         <v>1</v>
       </c>
-      <c r="C1406" s="13"/>
+      <c r="C1406" s="16"/>
     </row>
     <row r="1407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1407" t="s">
@@ -19298,7 +19061,7 @@
       <c r="B1407">
         <v>1</v>
       </c>
-      <c r="C1407" s="13"/>
+      <c r="C1407" s="16"/>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1408" t="s">
@@ -19307,7 +19070,7 @@
       <c r="B1408">
         <v>5</v>
       </c>
-      <c r="C1408" s="13"/>
+      <c r="C1408" s="16"/>
     </row>
     <row r="1409" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1409" t="s">
@@ -19352,12 +19115,12 @@
         <v>2330</v>
       </c>
       <c r="D1413" s="6"/>
-      <c r="S1413" s="11" t="s">
+      <c r="S1413" s="14" t="s">
         <v>2329</v>
       </c>
-      <c r="T1413" s="12"/>
-      <c r="U1413" s="12"/>
-      <c r="V1413" s="12"/>
+      <c r="T1413" s="15"/>
+      <c r="U1413" s="15"/>
+      <c r="V1413" s="15"/>
     </row>
     <row r="1414" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1414" t="s">
@@ -19487,10 +19250,10 @@
       <c r="B1428">
         <v>7</v>
       </c>
-      <c r="C1428" s="9">
+      <c r="C1428" s="13">
         <v>6</v>
       </c>
-      <c r="D1428" s="9"/>
+      <c r="D1428" s="13"/>
     </row>
     <row r="1429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1429" t="s">
@@ -19515,10 +19278,10 @@
       <c r="B1431">
         <v>11</v>
       </c>
-      <c r="C1431" s="9">
+      <c r="C1431" s="13">
         <v>5</v>
       </c>
-      <c r="D1431" s="9"/>
+      <c r="D1431" s="13"/>
     </row>
     <row r="1432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1432" t="s">
@@ -19535,10 +19298,10 @@
       <c r="B1433">
         <v>8</v>
       </c>
-      <c r="C1433" s="9">
+      <c r="C1433" s="13">
         <v>4</v>
       </c>
-      <c r="D1433" s="9"/>
+      <c r="D1433" s="13"/>
     </row>
     <row r="1434" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1434" t="s">
@@ -19563,10 +19326,10 @@
       <c r="B1436">
         <v>14</v>
       </c>
-      <c r="C1436" s="9">
+      <c r="C1436" s="13">
         <v>3</v>
       </c>
-      <c r="D1436" s="9"/>
+      <c r="D1436" s="13"/>
     </row>
     <row r="1437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1437" t="s">
@@ -19607,10 +19370,10 @@
       <c r="B1441">
         <v>7</v>
       </c>
-      <c r="C1441" s="9" t="s">
+      <c r="C1441" s="13" t="s">
         <v>2324</v>
       </c>
-      <c r="D1441" s="9"/>
+      <c r="D1441" s="13"/>
     </row>
     <row r="1442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1442" t="s">
@@ -19619,10 +19382,10 @@
       <c r="B1442">
         <v>1</v>
       </c>
-      <c r="C1442" s="9" t="s">
+      <c r="C1442" s="13" t="s">
         <v>2323</v>
       </c>
-      <c r="D1442" s="9"/>
+      <c r="D1442" s="13"/>
     </row>
     <row r="1443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1443" t="s">
@@ -19631,8 +19394,8 @@
       <c r="B1443">
         <v>1</v>
       </c>
-      <c r="C1443" s="9"/>
-      <c r="D1443" s="9"/>
+      <c r="C1443" s="13"/>
+      <c r="D1443" s="13"/>
     </row>
     <row r="1444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1444" t="s">
@@ -19641,8 +19404,8 @@
       <c r="B1444">
         <v>1</v>
       </c>
-      <c r="C1444" s="9"/>
-      <c r="D1444" s="9"/>
+      <c r="C1444" s="13"/>
+      <c r="D1444" s="13"/>
     </row>
     <row r="1445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1445" t="s">
@@ -19651,8 +19414,8 @@
       <c r="B1445">
         <v>1</v>
       </c>
-      <c r="C1445" s="9"/>
-      <c r="D1445" s="9"/>
+      <c r="C1445" s="13"/>
+      <c r="D1445" s="13"/>
     </row>
     <row r="1446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1446" t="s">
@@ -19661,8 +19424,8 @@
       <c r="B1446">
         <v>1</v>
       </c>
-      <c r="C1446" s="9"/>
-      <c r="D1446" s="9"/>
+      <c r="C1446" s="13"/>
+      <c r="D1446" s="13"/>
     </row>
     <row r="1447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1447" t="s">
@@ -19719,10 +19482,10 @@
       <c r="B1453">
         <v>13</v>
       </c>
-      <c r="C1453" s="9">
-        <v>1</v>
-      </c>
-      <c r="D1453" s="9"/>
+      <c r="C1453" s="13">
+        <v>1</v>
+      </c>
+      <c r="D1453" s="13"/>
     </row>
     <row r="1454" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1454" t="s">
@@ -19747,10 +19510,10 @@
       <c r="B1456">
         <v>10</v>
       </c>
-      <c r="C1456" s="9">
-        <v>1</v>
-      </c>
-      <c r="D1456" s="9"/>
+      <c r="C1456" s="13">
+        <v>1</v>
+      </c>
+      <c r="D1456" s="13"/>
     </row>
     <row r="1457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1457" t="s">
@@ -19775,10 +19538,10 @@
       <c r="B1459">
         <v>17</v>
       </c>
-      <c r="C1459" s="9">
-        <v>1</v>
-      </c>
-      <c r="D1459" s="9"/>
+      <c r="C1459" s="13">
+        <v>1</v>
+      </c>
+      <c r="D1459" s="13"/>
     </row>
     <row r="1460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1460" t="s">
@@ -19787,10 +19550,10 @@
       <c r="B1460">
         <v>3</v>
       </c>
-      <c r="C1460" s="9">
-        <v>1</v>
-      </c>
-      <c r="D1460" s="9"/>
+      <c r="C1460" s="13">
+        <v>1</v>
+      </c>
+      <c r="D1460" s="13"/>
     </row>
     <row r="1461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1461" t="s">
@@ -19799,8 +19562,8 @@
       <c r="B1461">
         <v>3</v>
       </c>
-      <c r="C1461" s="9"/>
-      <c r="D1461" s="9"/>
+      <c r="C1461" s="13"/>
+      <c r="D1461" s="13"/>
     </row>
     <row r="1462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1462" t="s">
@@ -19809,8 +19572,8 @@
       <c r="B1462">
         <v>2</v>
       </c>
-      <c r="C1462" s="9"/>
-      <c r="D1462" s="9"/>
+      <c r="C1462" s="13"/>
+      <c r="D1462" s="13"/>
     </row>
     <row r="1463" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1463" t="s">
@@ -19819,8 +19582,8 @@
       <c r="B1463">
         <v>2</v>
       </c>
-      <c r="C1463" s="9"/>
-      <c r="D1463" s="9"/>
+      <c r="C1463" s="13"/>
+      <c r="D1463" s="13"/>
     </row>
     <row r="1464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1464" t="s">
@@ -19829,10 +19592,10 @@
       <c r="B1464">
         <v>1</v>
       </c>
-      <c r="C1464" s="9">
-        <v>1</v>
-      </c>
-      <c r="D1464" s="9"/>
+      <c r="C1464" s="13">
+        <v>1</v>
+      </c>
+      <c r="D1464" s="13"/>
     </row>
     <row r="1465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1465" t="s">
@@ -19841,8 +19604,8 @@
       <c r="B1465">
         <v>2</v>
       </c>
-      <c r="C1465" s="9"/>
-      <c r="D1465" s="9"/>
+      <c r="C1465" s="13"/>
+      <c r="D1465" s="13"/>
     </row>
     <row r="1466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1466" t="s">
@@ -19851,8 +19614,8 @@
       <c r="B1466">
         <v>1</v>
       </c>
-      <c r="C1466" s="9"/>
-      <c r="D1466" s="9"/>
+      <c r="C1466" s="13"/>
+      <c r="D1466" s="13"/>
     </row>
     <row r="1467" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1467" t="s">
@@ -19861,8 +19624,8 @@
       <c r="B1467">
         <v>1</v>
       </c>
-      <c r="C1467" s="9"/>
-      <c r="D1467" s="9"/>
+      <c r="C1467" s="13"/>
+      <c r="D1467" s="13"/>
     </row>
     <row r="1468" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1468" t="s">
@@ -26710,21 +26473,16 @@
     <sortCondition descending="1" ref="A1:A2322"/>
   </sortState>
   <mergeCells count="23">
-    <mergeCell ref="N1362:N1363"/>
-    <mergeCell ref="C1355:C1362"/>
-    <mergeCell ref="D1356:D1361"/>
-    <mergeCell ref="E1357:E1360"/>
-    <mergeCell ref="F1358:F1359"/>
+    <mergeCell ref="C1383:C1388"/>
+    <mergeCell ref="S1413:V1413"/>
+    <mergeCell ref="C1402:C1408"/>
+    <mergeCell ref="G1390:AA1390"/>
+    <mergeCell ref="H1392:K1392"/>
     <mergeCell ref="C1460:D1463"/>
     <mergeCell ref="C1428:D1428"/>
     <mergeCell ref="C1464:D1467"/>
     <mergeCell ref="C1399:C1401"/>
     <mergeCell ref="C1395:C1398"/>
-    <mergeCell ref="C1383:C1388"/>
-    <mergeCell ref="S1413:V1413"/>
-    <mergeCell ref="C1402:C1408"/>
-    <mergeCell ref="G1390:AA1390"/>
-    <mergeCell ref="H1392:K1392"/>
     <mergeCell ref="C1459:D1459"/>
     <mergeCell ref="C1456:D1456"/>
     <mergeCell ref="C1453:D1453"/>
@@ -26733,6 +26491,11 @@
     <mergeCell ref="C1436:D1436"/>
     <mergeCell ref="C1433:D1433"/>
     <mergeCell ref="C1431:D1431"/>
+    <mergeCell ref="N1362:N1363"/>
+    <mergeCell ref="C1355:C1362"/>
+    <mergeCell ref="D1356:D1361"/>
+    <mergeCell ref="E1357:E1360"/>
+    <mergeCell ref="F1358:F1359"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
